--- a/Result/checksun_type/監理法遵.xlsx
+++ b/Result/checksun_type/監理法遵.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>45.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>48.57</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>48.57</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>923.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>639.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>639.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>649.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>966.14</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>966.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-131.9181011073526</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>923</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>923.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>43.41</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>519.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>498.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>498.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1102.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1091.02</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1091.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-165.5805573496141</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>519</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>519.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>43.54</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>45.86</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48.95</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>44.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>645.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>645.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1107.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1099.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1099.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-164.4704749332157</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>44</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>44.15</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>46.21</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>957.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>797.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>797</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1146.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1109.02</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1109.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-106.1178402336029</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>957</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>957.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>45.15</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>46.53</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>49.32</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>49.32</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>753.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>692.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>692.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1094.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1124.12</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1124.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-116.7884392258132</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>753</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>753.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>45.91</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>46.82</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>49.48</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>49.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>221.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>660.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>660</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1132.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1171.46</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1171.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-106.003993528049</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>221</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>221.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>46.72</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>49.68</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>49.68</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1253.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1705.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1705.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1264.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1197.88</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1197.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-29.8117856195272</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1253</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1253.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>47.47000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>49.89</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>49.89</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>801.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1569.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1569.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1197.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1178.44</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1178.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-30.47249626379858</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>801</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>801.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>47.98999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>50.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>50.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>434.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1496.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1496.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1365.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1182.34</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1182.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>18.10050625380677</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>434</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>434.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>47.45</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>47.81</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>50.12</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>50.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>591.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1496.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1496</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1788.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1213.76</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1213.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>126.1654917698927</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>591</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>591.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>47.42</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>50.23</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>50.23</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5449.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1605.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1605.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1990.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1227.62</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1227.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>259.2167035153764</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5449</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5449.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>49.86</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>50.07</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>50.19</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>50.19</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>6043261.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6105099.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6105099</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>7822471.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>9178525.18</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>9178525.18</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1033905.827351614</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>6043261</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>6043261.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>49.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>50.13</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>50.2</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>3022215.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>6473969.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>6473969.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>8355094.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>9901090.28</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>9901090.279999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1020766.573750045</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>3022215</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>3022215.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>49.08</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>50.21</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>50.24</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>50.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>7248657.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>7998691.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>7998691.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>9177973.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>12040565.8</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>12040565.8</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-641856.7623995896</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>7248657</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>7248657.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>48.9</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>50.26</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>50.25</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>50.25</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>6147212.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>9326443.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>9326443.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>12732824.4</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>12054329.28</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>12054329.28</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-530466.6475275233</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>6147212</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>6147212.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>48.99</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>50.32</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>50.26</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>50.26</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>8064150.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>9378665.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>9378665.199999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>13971591.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>12142511.2</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>12142511.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-234380.7102985885</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>8064150</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>8064150.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>49.11</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>50.39</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>50.26</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>50.26</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>7887612.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>9539843.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>9539843.800000001</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>13740567.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>12156901.5</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>12156901.5</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-8416.27460373193</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>7887612</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>7887612.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>49.85</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>50.55</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>50.32</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>50.32</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>10645825.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>10236219.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>10236219.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>13789352.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>12124535.46</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>12124535.46</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>333605.4290533364</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>10645825</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>10645825.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>50.47000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.65</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>50.36</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>50.36</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>13887418.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>10357256.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>10357256</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>13306761.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>12099052.72</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>12099052.72</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>514770.561811531</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>13887418</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>13887418.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>51.16</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.71</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>50.39</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>50.39</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>6408321.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>16139205.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>16139205.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>12477768.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>12053133.32</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>12053133.32</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>407879.6956871115</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>6408321</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>6408321.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>50.95999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>50.71</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>50.38</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>8870043.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>18564518.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>18564518.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>12247692.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>12443630.22</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>12443630.22</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>1041943.147806257</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>8870043</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>8870043.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>50.82</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>50.67</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>50.38</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>11369490.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>17941290.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>17941290.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>11937978.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>12656395.32</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>12656395.32</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>1646779.895554814</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>11369490</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>11369490.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>54.78</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>58.02</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>58.02</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>16370637.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>14968564.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>14968564.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>25991927.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>55328963.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>55328963.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-3761738.343921479</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>16370637</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>16370637.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>58.25</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>14210191.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>15743790.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>15743790.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>25956465.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>65312254.98</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>65312254.98</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-3880161.860334959</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>14210191</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>14210191.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>55.27</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>15825778.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>21316600.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>21316600.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>25649746.9</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>67714501.66</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>67714501.66</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-3679284.745913677</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>15825778</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>15825778.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>52.14</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>58.66</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>17027345.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>22754558.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>22754558</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>26782636.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>69191727.6</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>69191727.59999999</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-3434013.020100649</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>17027345</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>17027345.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>58.83</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>11408872.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>28718377.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>28718377.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>27355481.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>69373581.34</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>69373581.34</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-3089720.839649871</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>11408872</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>11408872.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>53.23999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>58.96</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>20246765.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>37015290.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>37015290.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>28888889.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>69945836.02</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>69945836.02</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1885548.444732688</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>20246765</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>20246765.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>54.21999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>59.12</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>42074242.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>36169141.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>36169141.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>29060387.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>70323701.58</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>70323701.58</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1044878.257539123</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>42074242</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>42074242.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>55.12</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>56.86</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>23015566.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>29982893.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>29982893.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>27325142.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>70871687.6</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>70871687.59999999</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-2145262.016636197</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>23015566</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>57.07</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>59.42</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>46846442.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>30810714.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>30810714.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>28427276.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>71965384.46</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>71965384.45999999</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1598621.314752154</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>46846442</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>59.56</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>52893437.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>25992585.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>25992585.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>25254632.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>72823093.42</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>72823093.42</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-3313920.550819516</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>52893437</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>56.66</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>59.68</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>59.68</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>16016019.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>20762488.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>20762488.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>23044675.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>73396602.94</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>73396602.94</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-6293886.04695791</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>16016019</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
